--- a/content/post/drafts/season-prediction/ladies_model-resursive-tests-actual_mae.xlsx
+++ b/content/post/drafts/season-prediction/ladies_model-resursive-tests-actual_mae.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">Polynomial</t>
   </si>
   <si>
+    <t xml:space="preserve">Random Forest</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Forest</t>
   </si>
   <si>
     <t xml:space="preserve">KNN</t>
@@ -509,25 +509,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.126932788844605</v>
+        <v>0.126143687513057</v>
       </c>
       <c r="C5" t="n">
-        <v>0.113443320594413</v>
+        <v>0.117179677025753</v>
       </c>
       <c r="D5" t="n">
-        <v>0.186856728834996</v>
+        <v>0.177376694602454</v>
       </c>
       <c r="E5" t="n">
-        <v>0.211772855609715</v>
+        <v>0.225113643933028</v>
       </c>
       <c r="F5" t="n">
-        <v>0.10172490951655</v>
+        <v>0.0959882445966517</v>
       </c>
       <c r="G5" t="n">
-        <v>0.108510931111433</v>
+        <v>0.104874645719477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.141540255751952</v>
+        <v>0.14111276556507</v>
       </c>
     </row>
     <row r="6">
@@ -535,25 +535,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>0.125139083925622</v>
+        <v>0.126932788844605</v>
       </c>
       <c r="C6" t="n">
-        <v>0.118659367858813</v>
+        <v>0.113443320594413</v>
       </c>
       <c r="D6" t="n">
-        <v>0.179014594950611</v>
+        <v>0.186856728834996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.222933692032589</v>
+        <v>0.211772855609715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.100527522143178</v>
+        <v>0.10172490951655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.105084055998448</v>
+        <v>0.108510931111433</v>
       </c>
       <c r="H6" t="n">
-        <v>0.14189305281821</v>
+        <v>0.141540255751952</v>
       </c>
     </row>
     <row r="7">
